--- a/templates/forms/LTC_Certification_Renewal_R8.4-.xlsx
+++ b/templates/forms/LTC_Certification_Renewal_R8.4-.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95675E84-6657-4E82-81F1-2AAF5DC81D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F8A4D3-07AF-4525-A76F-E30E0A4DBACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新規・更新" sheetId="33" r:id="rId1"/>
@@ -2558,6 +2558,672 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2567,9 +3233,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2591,9 +3254,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2603,9 +3263,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2627,671 +3284,14 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3797,9 +3797,9 @@
       <c r="V1" s="72"/>
       <c r="W1" s="72"/>
       <c r="X1" s="72"/>
-      <c r="AD1" s="160"/>
-      <c r="AE1" s="160"/>
-      <c r="AF1" s="160"/>
+      <c r="AD1" s="225"/>
+      <c r="AE1" s="225"/>
+      <c r="AF1" s="225"/>
     </row>
     <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="73" t="s">
@@ -3826,64 +3826,64 @@
       <c r="V2" s="72"/>
       <c r="W2" s="72"/>
       <c r="X2" s="72"/>
-      <c r="AD2" s="160"/>
-      <c r="AE2" s="160"/>
-      <c r="AF2" s="160"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="225"/>
     </row>
     <row r="3" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="161" t="s">
+      <c r="B3" s="226" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-      <c r="L3" s="161"/>
-      <c r="M3" s="161"/>
-      <c r="N3" s="161"/>
-      <c r="O3" s="161"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="161"/>
-      <c r="S3" s="161"/>
-      <c r="T3" s="161"/>
-      <c r="U3" s="161"/>
-      <c r="V3" s="161"/>
-      <c r="W3" s="161"/>
-      <c r="X3" s="161"/>
+      <c r="C3" s="226"/>
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="226"/>
+      <c r="H3" s="226"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="226"/>
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="226"/>
+      <c r="O3" s="226"/>
+      <c r="P3" s="226"/>
+      <c r="Q3" s="226"/>
+      <c r="R3" s="226"/>
+      <c r="S3" s="226"/>
+      <c r="T3" s="226"/>
+      <c r="U3" s="226"/>
+      <c r="V3" s="226"/>
+      <c r="W3" s="226"/>
+      <c r="X3" s="226"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
     <row r="4" spans="1:37" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="161"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="161"/>
-      <c r="P4" s="161"/>
-      <c r="Q4" s="161"/>
-      <c r="R4" s="161"/>
-      <c r="S4" s="161"/>
-      <c r="T4" s="161"/>
-      <c r="U4" s="161"/>
-      <c r="V4" s="161"/>
-      <c r="W4" s="161"/>
-      <c r="X4" s="161"/>
+      <c r="B4" s="226"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="226"/>
+      <c r="O4" s="226"/>
+      <c r="P4" s="226"/>
+      <c r="Q4" s="226"/>
+      <c r="R4" s="226"/>
+      <c r="S4" s="226"/>
+      <c r="T4" s="226"/>
+      <c r="U4" s="226"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="226"/>
+      <c r="X4" s="226"/>
       <c r="Y4" s="46"/>
       <c r="Z4" s="46"/>
       <c r="AC4" s="63"/>
@@ -3894,29 +3894,29 @@
       <c r="AF4" s="68"/>
     </row>
     <row r="5" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="161"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
-      <c r="O5" s="161"/>
-      <c r="P5" s="161"/>
-      <c r="Q5" s="161"/>
-      <c r="R5" s="161"/>
-      <c r="S5" s="161"/>
-      <c r="T5" s="161"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="161"/>
-      <c r="W5" s="161"/>
-      <c r="X5" s="161"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="226"/>
+      <c r="P5" s="226"/>
+      <c r="Q5" s="226"/>
+      <c r="R5" s="226"/>
+      <c r="S5" s="226"/>
+      <c r="T5" s="226"/>
+      <c r="U5" s="226"/>
+      <c r="V5" s="226"/>
+      <c r="W5" s="226"/>
+      <c r="X5" s="226"/>
       <c r="AC5" s="63"/>
       <c r="AD5" s="66"/>
       <c r="AF5" s="63"/>
@@ -3985,164 +3985,164 @@
       <c r="Q7" s="23"/>
       <c r="R7" s="23"/>
       <c r="S7" s="24"/>
-      <c r="T7" s="130" t="s">
+      <c r="T7" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="131"/>
-      <c r="X7" s="147"/>
-      <c r="Y7" s="148"/>
-      <c r="Z7" s="148"/>
-      <c r="AA7" s="148"/>
-      <c r="AB7" s="148"/>
-      <c r="AC7" s="148"/>
-      <c r="AD7" s="148"/>
-      <c r="AE7" s="148"/>
-      <c r="AF7" s="149"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="221"/>
+      <c r="X7" s="296"/>
+      <c r="Y7" s="297"/>
+      <c r="Z7" s="297"/>
+      <c r="AA7" s="297"/>
+      <c r="AB7" s="297"/>
+      <c r="AC7" s="297"/>
+      <c r="AD7" s="297"/>
+      <c r="AE7" s="297"/>
+      <c r="AF7" s="298"/>
       <c r="AI7" s="21"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="79"/>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="121" t="s">
+      <c r="A8" s="280" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="122"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="153" t="s">
+      <c r="B8" s="180"/>
+      <c r="C8" s="281"/>
+      <c r="D8" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
-      <c r="S8" s="139"/>
-      <c r="T8" s="132"/>
-      <c r="U8" s="132"/>
-      <c r="V8" s="132"/>
-      <c r="W8" s="133"/>
-      <c r="X8" s="150"/>
-      <c r="Y8" s="151"/>
-      <c r="Z8" s="151"/>
-      <c r="AA8" s="151"/>
-      <c r="AB8" s="151"/>
-      <c r="AC8" s="151"/>
-      <c r="AD8" s="151"/>
-      <c r="AE8" s="151"/>
-      <c r="AF8" s="152"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="287"/>
+      <c r="I8" s="287"/>
+      <c r="J8" s="287"/>
+      <c r="K8" s="287"/>
+      <c r="L8" s="287"/>
+      <c r="M8" s="287"/>
+      <c r="N8" s="287"/>
+      <c r="O8" s="287"/>
+      <c r="P8" s="287"/>
+      <c r="Q8" s="287"/>
+      <c r="R8" s="287"/>
+      <c r="S8" s="288"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="W8" s="97"/>
+      <c r="X8" s="299"/>
+      <c r="Y8" s="300"/>
+      <c r="Z8" s="300"/>
+      <c r="AA8" s="300"/>
+      <c r="AB8" s="300"/>
+      <c r="AC8" s="300"/>
+      <c r="AD8" s="300"/>
+      <c r="AE8" s="300"/>
+      <c r="AF8" s="301"/>
       <c r="AI8" s="21"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="79"/>
     </row>
     <row r="9" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="155" t="s">
+      <c r="A9" s="282"/>
+      <c r="B9" s="283"/>
+      <c r="C9" s="284"/>
+      <c r="D9" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144"/>
-      <c r="K9" s="144"/>
-      <c r="L9" s="144"/>
-      <c r="M9" s="144"/>
-      <c r="N9" s="144"/>
-      <c r="O9" s="144"/>
-      <c r="P9" s="144"/>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144"/>
-      <c r="T9" s="145" t="s">
+      <c r="E9" s="303"/>
+      <c r="F9" s="303"/>
+      <c r="G9" s="293"/>
+      <c r="H9" s="293"/>
+      <c r="I9" s="293"/>
+      <c r="J9" s="293"/>
+      <c r="K9" s="293"/>
+      <c r="L9" s="293"/>
+      <c r="M9" s="293"/>
+      <c r="N9" s="293"/>
+      <c r="O9" s="293"/>
+      <c r="P9" s="293"/>
+      <c r="Q9" s="293"/>
+      <c r="R9" s="293"/>
+      <c r="S9" s="293"/>
+      <c r="T9" s="294" t="s">
         <v>9</v>
       </c>
-      <c r="U9" s="145"/>
-      <c r="V9" s="145"/>
-      <c r="W9" s="145"/>
-      <c r="X9" s="146"/>
-      <c r="Y9" s="146"/>
-      <c r="Z9" s="146"/>
-      <c r="AA9" s="146"/>
-      <c r="AB9" s="146"/>
-      <c r="AC9" s="146"/>
-      <c r="AD9" s="146"/>
-      <c r="AE9" s="146"/>
-      <c r="AF9" s="146"/>
+      <c r="U9" s="294"/>
+      <c r="V9" s="294"/>
+      <c r="W9" s="294"/>
+      <c r="X9" s="295"/>
+      <c r="Y9" s="295"/>
+      <c r="Z9" s="295"/>
+      <c r="AA9" s="295"/>
+      <c r="AB9" s="295"/>
+      <c r="AC9" s="295"/>
+      <c r="AD9" s="295"/>
+      <c r="AE9" s="295"/>
+      <c r="AF9" s="295"/>
       <c r="AI9" s="21"/>
       <c r="AJ9" s="27"/>
       <c r="AK9" s="27"/>
     </row>
     <row r="10" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="182" t="s">
+      <c r="A10" s="282"/>
+      <c r="B10" s="283"/>
+      <c r="C10" s="284"/>
+      <c r="D10" s="238" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="183"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="144"/>
-      <c r="L10" s="144"/>
-      <c r="M10" s="144"/>
-      <c r="N10" s="144"/>
-      <c r="O10" s="144"/>
-      <c r="P10" s="144"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="145"/>
-      <c r="U10" s="145"/>
-      <c r="V10" s="145"/>
-      <c r="W10" s="145"/>
-      <c r="X10" s="146"/>
-      <c r="Y10" s="146"/>
-      <c r="Z10" s="146"/>
-      <c r="AA10" s="146"/>
-      <c r="AB10" s="146"/>
-      <c r="AC10" s="146"/>
-      <c r="AD10" s="146"/>
-      <c r="AE10" s="146"/>
-      <c r="AF10" s="146"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="293"/>
+      <c r="H10" s="293"/>
+      <c r="I10" s="293"/>
+      <c r="J10" s="293"/>
+      <c r="K10" s="293"/>
+      <c r="L10" s="293"/>
+      <c r="M10" s="293"/>
+      <c r="N10" s="293"/>
+      <c r="O10" s="293"/>
+      <c r="P10" s="293"/>
+      <c r="Q10" s="293"/>
+      <c r="R10" s="293"/>
+      <c r="S10" s="293"/>
+      <c r="T10" s="294"/>
+      <c r="U10" s="294"/>
+      <c r="V10" s="294"/>
+      <c r="W10" s="294"/>
+      <c r="X10" s="295"/>
+      <c r="Y10" s="295"/>
+      <c r="Z10" s="295"/>
+      <c r="AA10" s="295"/>
+      <c r="AB10" s="295"/>
+      <c r="AC10" s="295"/>
+      <c r="AD10" s="295"/>
+      <c r="AE10" s="295"/>
+      <c r="AF10" s="295"/>
       <c r="AI10" s="21"/>
       <c r="AJ10" s="27"/>
       <c r="AK10" s="27"/>
     </row>
     <row r="11" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="155" t="s">
+      <c r="A11" s="282"/>
+      <c r="B11" s="283"/>
+      <c r="C11" s="284"/>
+      <c r="D11" s="302" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="221"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="134" t="s">
+      <c r="E11" s="304"/>
+      <c r="F11" s="305"/>
+      <c r="G11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
-      <c r="L11" s="135"/>
-      <c r="M11" s="135"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
       <c r="N11" s="59" t="s">
         <v>64</v>
       </c>
@@ -4167,26 +4167,26 @@
       <c r="AK11" s="27"/>
     </row>
     <row r="12" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="127"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="182" t="s">
+      <c r="A12" s="285"/>
+      <c r="B12" s="264"/>
+      <c r="C12" s="265"/>
+      <c r="D12" s="238" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="223"/>
-      <c r="F12" s="224"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="132"/>
+      <c r="E12" s="306"/>
+      <c r="F12" s="307"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
       <c r="S12" s="32"/>
       <c r="T12" s="32"/>
       <c r="U12" s="32" t="s">
@@ -4194,92 +4194,92 @@
       </c>
       <c r="V12" s="32"/>
       <c r="W12" s="32"/>
-      <c r="X12" s="132"/>
-      <c r="Y12" s="132"/>
-      <c r="Z12" s="132"/>
-      <c r="AA12" s="132"/>
-      <c r="AB12" s="132"/>
-      <c r="AC12" s="132"/>
-      <c r="AD12" s="132"/>
-      <c r="AE12" s="132"/>
-      <c r="AF12" s="143"/>
+      <c r="X12" s="96"/>
+      <c r="Y12" s="96"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="96"/>
+      <c r="AB12" s="96"/>
+      <c r="AC12" s="96"/>
+      <c r="AD12" s="96"/>
+      <c r="AE12" s="96"/>
+      <c r="AF12" s="292"/>
       <c r="AK12" s="27"/>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="176" t="s">
+      <c r="A13" s="235" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="177"/>
-      <c r="C13" s="177"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="179" t="s">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="334" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="180"/>
-      <c r="I13" s="180"/>
-      <c r="J13" s="180"/>
-      <c r="K13" s="180"/>
-      <c r="L13" s="180"/>
-      <c r="M13" s="180"/>
-      <c r="N13" s="180"/>
-      <c r="O13" s="180"/>
-      <c r="P13" s="180"/>
-      <c r="Q13" s="180"/>
-      <c r="R13" s="180"/>
-      <c r="S13" s="180"/>
-      <c r="T13" s="180"/>
-      <c r="U13" s="180"/>
-      <c r="V13" s="180"/>
-      <c r="W13" s="180"/>
-      <c r="X13" s="180"/>
-      <c r="Y13" s="180"/>
-      <c r="Z13" s="180"/>
-      <c r="AA13" s="180"/>
-      <c r="AB13" s="180"/>
-      <c r="AC13" s="180"/>
-      <c r="AD13" s="180"/>
-      <c r="AE13" s="180"/>
-      <c r="AF13" s="181"/>
+      <c r="H13" s="335"/>
+      <c r="I13" s="335"/>
+      <c r="J13" s="335"/>
+      <c r="K13" s="335"/>
+      <c r="L13" s="335"/>
+      <c r="M13" s="335"/>
+      <c r="N13" s="335"/>
+      <c r="O13" s="335"/>
+      <c r="P13" s="335"/>
+      <c r="Q13" s="335"/>
+      <c r="R13" s="335"/>
+      <c r="S13" s="335"/>
+      <c r="T13" s="335"/>
+      <c r="U13" s="335"/>
+      <c r="V13" s="335"/>
+      <c r="W13" s="335"/>
+      <c r="X13" s="335"/>
+      <c r="Y13" s="335"/>
+      <c r="Z13" s="335"/>
+      <c r="AA13" s="335"/>
+      <c r="AB13" s="335"/>
+      <c r="AC13" s="335"/>
+      <c r="AD13" s="335"/>
+      <c r="AE13" s="335"/>
+      <c r="AF13" s="336"/>
     </row>
     <row r="14" spans="1:37" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="117" t="s">
+      <c r="A14" s="276" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="120" t="s">
+      <c r="B14" s="277"/>
+      <c r="C14" s="277"/>
+      <c r="D14" s="277"/>
+      <c r="E14" s="277"/>
+      <c r="F14" s="278"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="277"/>
+      <c r="I14" s="277"/>
+      <c r="J14" s="277"/>
+      <c r="K14" s="277"/>
+      <c r="L14" s="277"/>
+      <c r="M14" s="277"/>
+      <c r="N14" s="277"/>
+      <c r="O14" s="277"/>
+      <c r="P14" s="278"/>
+      <c r="Q14" s="279" t="s">
         <v>17</v>
       </c>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
-      <c r="U14" s="118"/>
-      <c r="V14" s="119"/>
-      <c r="W14" s="140"/>
-      <c r="X14" s="141"/>
-      <c r="Y14" s="141"/>
-      <c r="Z14" s="141"/>
-      <c r="AA14" s="141"/>
-      <c r="AB14" s="141"/>
-      <c r="AC14" s="141"/>
-      <c r="AD14" s="141"/>
-      <c r="AE14" s="141"/>
-      <c r="AF14" s="142"/>
+      <c r="R14" s="277"/>
+      <c r="S14" s="277"/>
+      <c r="T14" s="277"/>
+      <c r="U14" s="277"/>
+      <c r="V14" s="278"/>
+      <c r="W14" s="289"/>
+      <c r="X14" s="290"/>
+      <c r="Y14" s="290"/>
+      <c r="Z14" s="290"/>
+      <c r="AA14" s="290"/>
+      <c r="AB14" s="290"/>
+      <c r="AC14" s="290"/>
+      <c r="AD14" s="290"/>
+      <c r="AE14" s="290"/>
+      <c r="AF14" s="291"/>
     </row>
     <row r="15" spans="1:37" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="32"/>
@@ -4318,32 +4318,32 @@
       <c r="AK15" s="10"/>
     </row>
     <row r="16" spans="1:37" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="278" t="s">
+      <c r="A16" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="248" t="s">
+      <c r="B16" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="248"/>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="260"/>
-      <c r="H16" s="261"/>
-      <c r="I16" s="261"/>
-      <c r="J16" s="261"/>
-      <c r="K16" s="261"/>
-      <c r="L16" s="261"/>
-      <c r="M16" s="261"/>
-      <c r="N16" s="261"/>
-      <c r="O16" s="261"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="249" t="s">
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="194"/>
+      <c r="H16" s="195"/>
+      <c r="I16" s="195"/>
+      <c r="J16" s="195"/>
+      <c r="K16" s="195"/>
+      <c r="L16" s="195"/>
+      <c r="M16" s="195"/>
+      <c r="N16" s="195"/>
+      <c r="O16" s="195"/>
+      <c r="P16" s="196"/>
+      <c r="Q16" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="250"/>
-      <c r="S16" s="250"/>
-      <c r="T16" s="251"/>
+      <c r="R16" s="183"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="184"/>
       <c r="U16" s="88"/>
       <c r="V16" s="88"/>
       <c r="W16" s="88"/>
@@ -4360,144 +4360,144 @@
       <c r="AK16" s="10"/>
     </row>
     <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="279"/>
-      <c r="B17" s="252" t="s">
+      <c r="A17" s="118"/>
+      <c r="B17" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="253"/>
-      <c r="D17" s="253"/>
-      <c r="E17" s="253"/>
-      <c r="F17" s="253"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="264"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
-      <c r="M17" s="264"/>
-      <c r="N17" s="264"/>
-      <c r="O17" s="264"/>
-      <c r="P17" s="265"/>
-      <c r="Q17" s="254" t="s">
+      <c r="C17" s="186"/>
+      <c r="D17" s="186"/>
+      <c r="E17" s="186"/>
+      <c r="F17" s="186"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
+      <c r="P17" s="145"/>
+      <c r="Q17" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="R17" s="255"/>
-      <c r="S17" s="255"/>
-      <c r="T17" s="256"/>
-      <c r="U17" s="168"/>
-      <c r="V17" s="169"/>
-      <c r="W17" s="169"/>
-      <c r="X17" s="169"/>
-      <c r="Y17" s="169"/>
-      <c r="Z17" s="169"/>
-      <c r="AA17" s="169"/>
-      <c r="AB17" s="169"/>
-      <c r="AC17" s="169"/>
-      <c r="AD17" s="169"/>
-      <c r="AE17" s="169"/>
-      <c r="AF17" s="170"/>
+      <c r="R17" s="188"/>
+      <c r="S17" s="188"/>
+      <c r="T17" s="189"/>
+      <c r="U17" s="107"/>
+      <c r="V17" s="108"/>
+      <c r="W17" s="108"/>
+      <c r="X17" s="108"/>
+      <c r="Y17" s="108"/>
+      <c r="Z17" s="108"/>
+      <c r="AA17" s="108"/>
+      <c r="AB17" s="108"/>
+      <c r="AC17" s="108"/>
+      <c r="AD17" s="108"/>
+      <c r="AE17" s="108"/>
+      <c r="AF17" s="233"/>
     </row>
     <row r="18" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="279"/>
-      <c r="B18" s="171" t="s">
+      <c r="A18" s="118"/>
+      <c r="B18" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="172"/>
-      <c r="D18" s="172"/>
-      <c r="E18" s="172"/>
-      <c r="F18" s="172"/>
-      <c r="G18" s="323"/>
-      <c r="H18" s="324"/>
-      <c r="I18" s="324"/>
-      <c r="J18" s="324"/>
-      <c r="K18" s="324"/>
-      <c r="L18" s="324"/>
-      <c r="M18" s="324"/>
-      <c r="N18" s="324"/>
-      <c r="O18" s="324"/>
-      <c r="P18" s="325"/>
-      <c r="Q18" s="173" t="s">
+      <c r="C18" s="234"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="197"/>
+      <c r="H18" s="198"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="198"/>
+      <c r="K18" s="198"/>
+      <c r="L18" s="198"/>
+      <c r="M18" s="198"/>
+      <c r="N18" s="198"/>
+      <c r="O18" s="198"/>
+      <c r="P18" s="199"/>
+      <c r="Q18" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="R18" s="174"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="175"/>
-      <c r="U18" s="225"/>
-      <c r="V18" s="226"/>
-      <c r="W18" s="226"/>
-      <c r="X18" s="226"/>
-      <c r="Y18" s="226"/>
-      <c r="Z18" s="226"/>
-      <c r="AA18" s="226"/>
-      <c r="AB18" s="226"/>
-      <c r="AC18" s="226"/>
-      <c r="AD18" s="226"/>
-      <c r="AE18" s="226"/>
-      <c r="AF18" s="227"/>
+      <c r="R18" s="175"/>
+      <c r="S18" s="175"/>
+      <c r="T18" s="176"/>
+      <c r="U18" s="308"/>
+      <c r="V18" s="309"/>
+      <c r="W18" s="309"/>
+      <c r="X18" s="309"/>
+      <c r="Y18" s="309"/>
+      <c r="Z18" s="309"/>
+      <c r="AA18" s="309"/>
+      <c r="AB18" s="309"/>
+      <c r="AC18" s="309"/>
+      <c r="AD18" s="309"/>
+      <c r="AE18" s="309"/>
+      <c r="AF18" s="310"/>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="279"/>
-      <c r="B19" s="175" t="s">
+      <c r="A19" s="118"/>
+      <c r="B19" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="257"/>
+      <c r="C19" s="190"/>
+      <c r="D19" s="190"/>
+      <c r="E19" s="190"/>
+      <c r="F19" s="191"/>
       <c r="G19" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="228"/>
-      <c r="I19" s="228"/>
-      <c r="J19" s="228"/>
-      <c r="K19" s="228"/>
-      <c r="L19" s="228"/>
+      <c r="H19" s="311"/>
+      <c r="I19" s="311"/>
+      <c r="J19" s="311"/>
+      <c r="K19" s="311"/>
+      <c r="L19" s="311"/>
       <c r="M19" s="57" t="s">
         <v>68</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="258" t="s">
+      <c r="O19" s="192" t="s">
         <v>52</v>
       </c>
-      <c r="P19" s="258"/>
-      <c r="Q19" s="258"/>
-      <c r="R19" s="258"/>
-      <c r="S19" s="258"/>
-      <c r="T19" s="258"/>
-      <c r="U19" s="258"/>
-      <c r="V19" s="258"/>
-      <c r="W19" s="258"/>
-      <c r="X19" s="258"/>
-      <c r="Y19" s="258"/>
-      <c r="Z19" s="258"/>
-      <c r="AA19" s="258"/>
-      <c r="AB19" s="258"/>
-      <c r="AC19" s="258"/>
-      <c r="AD19" s="258"/>
-      <c r="AE19" s="258"/>
-      <c r="AF19" s="259"/>
+      <c r="P19" s="192"/>
+      <c r="Q19" s="192"/>
+      <c r="R19" s="192"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="192"/>
+      <c r="U19" s="192"/>
+      <c r="V19" s="192"/>
+      <c r="W19" s="192"/>
+      <c r="X19" s="192"/>
+      <c r="Y19" s="192"/>
+      <c r="Z19" s="192"/>
+      <c r="AA19" s="192"/>
+      <c r="AB19" s="192"/>
+      <c r="AC19" s="192"/>
+      <c r="AD19" s="192"/>
+      <c r="AE19" s="192"/>
+      <c r="AF19" s="193"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="279"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="257"/>
-      <c r="G20" s="229"/>
-      <c r="H20" s="230"/>
-      <c r="I20" s="230"/>
-      <c r="J20" s="230"/>
-      <c r="K20" s="230"/>
-      <c r="L20" s="230"/>
-      <c r="M20" s="230"/>
-      <c r="N20" s="230"/>
-      <c r="O20" s="230"/>
-      <c r="P20" s="230"/>
-      <c r="Q20" s="230"/>
-      <c r="R20" s="230"/>
-      <c r="S20" s="230"/>
-      <c r="T20" s="230"/>
+      <c r="A20" s="118"/>
+      <c r="B20" s="176"/>
+      <c r="C20" s="190"/>
+      <c r="D20" s="190"/>
+      <c r="E20" s="190"/>
+      <c r="F20" s="191"/>
+      <c r="G20" s="312"/>
+      <c r="H20" s="313"/>
+      <c r="I20" s="313"/>
+      <c r="J20" s="313"/>
+      <c r="K20" s="313"/>
+      <c r="L20" s="313"/>
+      <c r="M20" s="313"/>
+      <c r="N20" s="313"/>
+      <c r="O20" s="313"/>
+      <c r="P20" s="313"/>
+      <c r="Q20" s="313"/>
+      <c r="R20" s="313"/>
+      <c r="S20" s="313"/>
+      <c r="T20" s="313"/>
       <c r="U20" s="90"/>
       <c r="V20" s="90"/>
       <c r="W20" s="90"/>
@@ -4511,312 +4511,312 @@
       <c r="AF20" s="5"/>
     </row>
     <row r="21" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="279"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="173"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="136"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="132"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="132"/>
-      <c r="T21" s="132"/>
-      <c r="U21" s="132" t="s">
+      <c r="A21" s="118"/>
+      <c r="B21" s="176"/>
+      <c r="C21" s="190"/>
+      <c r="D21" s="190"/>
+      <c r="E21" s="190"/>
+      <c r="F21" s="191"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="96"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="96"/>
+      <c r="U21" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="132"/>
-      <c r="W21" s="132"/>
-      <c r="X21" s="132"/>
-      <c r="Y21" s="132"/>
-      <c r="Z21" s="132"/>
-      <c r="AA21" s="132"/>
-      <c r="AB21" s="132"/>
-      <c r="AC21" s="132"/>
-      <c r="AD21" s="132"/>
-      <c r="AE21" s="132"/>
-      <c r="AF21" s="143"/>
+      <c r="V21" s="96"/>
+      <c r="W21" s="96"/>
+      <c r="X21" s="96"/>
+      <c r="Y21" s="96"/>
+      <c r="Z21" s="96"/>
+      <c r="AA21" s="96"/>
+      <c r="AB21" s="96"/>
+      <c r="AC21" s="96"/>
+      <c r="AD21" s="96"/>
+      <c r="AE21" s="96"/>
+      <c r="AF21" s="292"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="279"/>
-      <c r="B22" s="210" t="s">
+      <c r="A22" s="118"/>
+      <c r="B22" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="210"/>
-      <c r="D22" s="210"/>
-      <c r="E22" s="210"/>
-      <c r="F22" s="171"/>
-      <c r="G22" s="295" t="s">
+      <c r="C22" s="200"/>
+      <c r="D22" s="200"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="201"/>
+      <c r="G22" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="296"/>
-      <c r="I22" s="296"/>
-      <c r="J22" s="297"/>
-      <c r="K22" s="263" t="s">
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="264"/>
-      <c r="M22" s="265"/>
-      <c r="N22" s="103"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="107"/>
-      <c r="S22" s="107"/>
-      <c r="T22" s="107"/>
-      <c r="U22" s="107"/>
-      <c r="V22" s="107"/>
-      <c r="W22" s="107"/>
-      <c r="X22" s="107"/>
-      <c r="Y22" s="107"/>
-      <c r="Z22" s="107"/>
-      <c r="AA22" s="107"/>
-      <c r="AB22" s="107"/>
-      <c r="AC22" s="107"/>
-      <c r="AD22" s="107"/>
-      <c r="AE22" s="107"/>
-      <c r="AF22" s="301"/>
+      <c r="L22" s="144"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="146"/>
+      <c r="O22" s="147"/>
+      <c r="P22" s="147"/>
+      <c r="Q22" s="147"/>
+      <c r="R22" s="147"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="147"/>
+      <c r="U22" s="147"/>
+      <c r="V22" s="147"/>
+      <c r="W22" s="147"/>
+      <c r="X22" s="147"/>
+      <c r="Y22" s="147"/>
+      <c r="Z22" s="147"/>
+      <c r="AA22" s="147"/>
+      <c r="AB22" s="147"/>
+      <c r="AC22" s="147"/>
+      <c r="AD22" s="147"/>
+      <c r="AE22" s="147"/>
+      <c r="AF22" s="148"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="279"/>
-      <c r="B23" s="266"/>
-      <c r="C23" s="266"/>
-      <c r="D23" s="266"/>
-      <c r="E23" s="266"/>
-      <c r="F23" s="267"/>
-      <c r="G23" s="298"/>
-      <c r="H23" s="299"/>
-      <c r="I23" s="299"/>
-      <c r="J23" s="300"/>
-      <c r="K23" s="263" t="s">
+      <c r="A23" s="118"/>
+      <c r="B23" s="202"/>
+      <c r="C23" s="202"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="141"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="264"/>
-      <c r="M23" s="265"/>
-      <c r="N23" s="103"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="107"/>
-      <c r="Q23" s="107"/>
-      <c r="R23" s="107"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="107"/>
-      <c r="U23" s="107"/>
+      <c r="L23" s="144"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="147"/>
+      <c r="P23" s="147"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
       <c r="V23" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="W23" s="107"/>
-      <c r="X23" s="107"/>
-      <c r="Y23" s="107"/>
-      <c r="Z23" s="107"/>
-      <c r="AA23" s="107"/>
-      <c r="AB23" s="107"/>
-      <c r="AC23" s="107"/>
-      <c r="AD23" s="107"/>
-      <c r="AE23" s="107"/>
-      <c r="AF23" s="301"/>
+      <c r="W23" s="147"/>
+      <c r="X23" s="147"/>
+      <c r="Y23" s="147"/>
+      <c r="Z23" s="147"/>
+      <c r="AA23" s="147"/>
+      <c r="AB23" s="147"/>
+      <c r="AC23" s="147"/>
+      <c r="AD23" s="147"/>
+      <c r="AE23" s="147"/>
+      <c r="AF23" s="148"/>
     </row>
     <row r="24" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="279"/>
-      <c r="B24" s="266"/>
-      <c r="C24" s="266"/>
-      <c r="D24" s="266"/>
-      <c r="E24" s="266"/>
-      <c r="F24" s="267"/>
-      <c r="G24" s="302" t="s">
+      <c r="A24" s="118"/>
+      <c r="B24" s="202"/>
+      <c r="C24" s="202"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="303"/>
-      <c r="I24" s="303"/>
-      <c r="J24" s="304"/>
-      <c r="K24" s="308" t="s">
+      <c r="H24" s="150"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="151"/>
+      <c r="K24" s="155" t="s">
         <v>70</v>
       </c>
-      <c r="L24" s="309"/>
-      <c r="M24" s="309"/>
-      <c r="N24" s="309"/>
-      <c r="O24" s="309"/>
-      <c r="P24" s="309"/>
-      <c r="Q24" s="309"/>
-      <c r="R24" s="309"/>
-      <c r="S24" s="310"/>
-      <c r="T24" s="310"/>
-      <c r="U24" s="310"/>
-      <c r="V24" s="310"/>
-      <c r="W24" s="310"/>
-      <c r="X24" s="310"/>
-      <c r="Y24" s="310"/>
-      <c r="Z24" s="310"/>
-      <c r="AA24" s="310"/>
-      <c r="AB24" s="310"/>
-      <c r="AC24" s="310"/>
-      <c r="AD24" s="310"/>
-      <c r="AE24" s="310"/>
-      <c r="AF24" s="311"/>
+      <c r="L24" s="156"/>
+      <c r="M24" s="156"/>
+      <c r="N24" s="156"/>
+      <c r="O24" s="156"/>
+      <c r="P24" s="156"/>
+      <c r="Q24" s="156"/>
+      <c r="R24" s="156"/>
+      <c r="S24" s="157"/>
+      <c r="T24" s="157"/>
+      <c r="U24" s="157"/>
+      <c r="V24" s="157"/>
+      <c r="W24" s="157"/>
+      <c r="X24" s="157"/>
+      <c r="Y24" s="157"/>
+      <c r="Z24" s="157"/>
+      <c r="AA24" s="157"/>
+      <c r="AB24" s="157"/>
+      <c r="AC24" s="157"/>
+      <c r="AD24" s="157"/>
+      <c r="AE24" s="157"/>
+      <c r="AF24" s="158"/>
     </row>
     <row r="25" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="279"/>
-      <c r="B25" s="169"/>
-      <c r="C25" s="169"/>
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="268"/>
-      <c r="G25" s="305"/>
-      <c r="H25" s="306"/>
-      <c r="I25" s="306"/>
-      <c r="J25" s="307"/>
-      <c r="K25" s="153" t="s">
+      <c r="A25" s="118"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="152"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="154"/>
-      <c r="M25" s="154"/>
-      <c r="N25" s="154"/>
-      <c r="O25" s="154"/>
-      <c r="P25" s="154"/>
-      <c r="Q25" s="154"/>
-      <c r="R25" s="154"/>
-      <c r="S25" s="154"/>
-      <c r="T25" s="154"/>
-      <c r="U25" s="154"/>
-      <c r="V25" s="154"/>
-      <c r="W25" s="115"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="115"/>
-      <c r="AC25" s="115"/>
-      <c r="AD25" s="115"/>
-      <c r="AE25" s="115"/>
-      <c r="AF25" s="116"/>
+      <c r="L25" s="160"/>
+      <c r="M25" s="160"/>
+      <c r="N25" s="160"/>
+      <c r="O25" s="160"/>
+      <c r="P25" s="160"/>
+      <c r="Q25" s="160"/>
+      <c r="R25" s="160"/>
+      <c r="S25" s="160"/>
+      <c r="T25" s="160"/>
+      <c r="U25" s="160"/>
+      <c r="V25" s="160"/>
+      <c r="W25" s="274"/>
+      <c r="X25" s="274"/>
+      <c r="Y25" s="274"/>
+      <c r="Z25" s="274"/>
+      <c r="AA25" s="274"/>
+      <c r="AB25" s="274"/>
+      <c r="AC25" s="274"/>
+      <c r="AD25" s="274"/>
+      <c r="AE25" s="274"/>
+      <c r="AF25" s="275"/>
     </row>
     <row r="26" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="279"/>
-      <c r="B26" s="95" t="s">
+      <c r="A26" s="118"/>
+      <c r="B26" s="214" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="100" t="s">
+      <c r="C26" s="317"/>
+      <c r="D26" s="317"/>
+      <c r="E26" s="317"/>
+      <c r="F26" s="318"/>
+      <c r="G26" s="321" t="s">
         <v>55</v>
       </c>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="103"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="107"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="107"/>
-      <c r="R26" s="107"/>
-      <c r="S26" s="107"/>
-      <c r="T26" s="107"/>
-      <c r="U26" s="108"/>
-      <c r="V26" s="105" t="s">
+      <c r="H26" s="322"/>
+      <c r="I26" s="322"/>
+      <c r="J26" s="322"/>
+      <c r="K26" s="322"/>
+      <c r="L26" s="323"/>
+      <c r="M26" s="146"/>
+      <c r="N26" s="147"/>
+      <c r="O26" s="147"/>
+      <c r="P26" s="147"/>
+      <c r="Q26" s="147"/>
+      <c r="R26" s="147"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="327"/>
+      <c r="V26" s="325" t="s">
         <v>57</v>
       </c>
-      <c r="W26" s="106"/>
-      <c r="X26" s="106"/>
-      <c r="Y26" s="106"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="109"/>
-      <c r="AB26" s="110"/>
-      <c r="AC26" s="110"/>
-      <c r="AD26" s="110"/>
-      <c r="AE26" s="110"/>
-      <c r="AF26" s="111"/>
+      <c r="W26" s="326"/>
+      <c r="X26" s="326"/>
+      <c r="Y26" s="326"/>
+      <c r="Z26" s="324"/>
+      <c r="AA26" s="328"/>
+      <c r="AB26" s="329"/>
+      <c r="AC26" s="329"/>
+      <c r="AD26" s="329"/>
+      <c r="AE26" s="329"/>
+      <c r="AF26" s="330"/>
       <c r="AJ26" s="57"/>
       <c r="AK26" s="8"/>
     </row>
     <row r="27" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="279"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="100" t="s">
+      <c r="A27" s="118"/>
+      <c r="B27" s="319"/>
+      <c r="C27" s="319"/>
+      <c r="D27" s="319"/>
+      <c r="E27" s="319"/>
+      <c r="F27" s="320"/>
+      <c r="G27" s="321" t="s">
         <v>59</v>
       </c>
-      <c r="H27" s="101"/>
-      <c r="I27" s="101"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="103" t="s">
+      <c r="H27" s="322"/>
+      <c r="I27" s="322"/>
+      <c r="J27" s="322"/>
+      <c r="K27" s="322"/>
+      <c r="L27" s="323"/>
+      <c r="M27" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="N27" s="104"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="113"/>
-      <c r="T27" s="113"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="103" t="s">
+      <c r="N27" s="324"/>
+      <c r="O27" s="331"/>
+      <c r="P27" s="332"/>
+      <c r="Q27" s="332"/>
+      <c r="R27" s="332"/>
+      <c r="S27" s="332"/>
+      <c r="T27" s="332"/>
+      <c r="U27" s="333"/>
+      <c r="V27" s="146" t="s">
         <v>58</v>
       </c>
-      <c r="W27" s="106"/>
-      <c r="X27" s="104"/>
-      <c r="Y27" s="109"/>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="110"/>
-      <c r="AB27" s="110"/>
-      <c r="AC27" s="110"/>
-      <c r="AD27" s="110"/>
-      <c r="AE27" s="110"/>
-      <c r="AF27" s="111"/>
+      <c r="W27" s="326"/>
+      <c r="X27" s="324"/>
+      <c r="Y27" s="328"/>
+      <c r="Z27" s="329"/>
+      <c r="AA27" s="329"/>
+      <c r="AB27" s="329"/>
+      <c r="AC27" s="329"/>
+      <c r="AD27" s="329"/>
+      <c r="AE27" s="329"/>
+      <c r="AF27" s="330"/>
       <c r="AJ27" s="57"/>
       <c r="AK27" s="8"/>
     </row>
     <row r="28" spans="1:37" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="279"/>
-      <c r="B28" s="95" t="s">
+      <c r="A28" s="118"/>
+      <c r="B28" s="214" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="207"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="93"/>
-      <c r="R28" s="93"/>
-      <c r="S28" s="93"/>
-      <c r="T28" s="93"/>
-      <c r="U28" s="93"/>
-      <c r="V28" s="93"/>
-      <c r="W28" s="93"/>
-      <c r="X28" s="93"/>
-      <c r="Y28" s="93"/>
-      <c r="Z28" s="93"/>
-      <c r="AA28" s="93"/>
-      <c r="AB28" s="93"/>
-      <c r="AC28" s="93"/>
-      <c r="AD28" s="93"/>
-      <c r="AE28" s="93"/>
-      <c r="AF28" s="94"/>
+      <c r="C28" s="214"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="214"/>
+      <c r="F28" s="215"/>
+      <c r="G28" s="314"/>
+      <c r="H28" s="315"/>
+      <c r="I28" s="315"/>
+      <c r="J28" s="315"/>
+      <c r="K28" s="315"/>
+      <c r="L28" s="315"/>
+      <c r="M28" s="315"/>
+      <c r="N28" s="315"/>
+      <c r="O28" s="315"/>
+      <c r="P28" s="315"/>
+      <c r="Q28" s="315"/>
+      <c r="R28" s="315"/>
+      <c r="S28" s="315"/>
+      <c r="T28" s="315"/>
+      <c r="U28" s="315"/>
+      <c r="V28" s="315"/>
+      <c r="W28" s="315"/>
+      <c r="X28" s="315"/>
+      <c r="Y28" s="315"/>
+      <c r="Z28" s="315"/>
+      <c r="AA28" s="315"/>
+      <c r="AB28" s="315"/>
+      <c r="AC28" s="315"/>
+      <c r="AD28" s="315"/>
+      <c r="AE28" s="315"/>
+      <c r="AF28" s="316"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
@@ -4824,40 +4824,40 @@
       <c r="AK28" s="50"/>
     </row>
     <row r="29" spans="1:37" s="21" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="280"/>
-      <c r="B29" s="276"/>
-      <c r="C29" s="276"/>
-      <c r="D29" s="276"/>
-      <c r="E29" s="276"/>
-      <c r="F29" s="277"/>
-      <c r="G29" s="273" t="s">
+      <c r="A29" s="119"/>
+      <c r="B29" s="216"/>
+      <c r="C29" s="216"/>
+      <c r="D29" s="216"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="274"/>
-      <c r="I29" s="274"/>
-      <c r="J29" s="274"/>
-      <c r="K29" s="274"/>
-      <c r="L29" s="274"/>
-      <c r="M29" s="274"/>
-      <c r="N29" s="274"/>
-      <c r="O29" s="274"/>
-      <c r="P29" s="274"/>
-      <c r="Q29" s="274"/>
-      <c r="R29" s="274"/>
-      <c r="S29" s="274"/>
-      <c r="T29" s="274"/>
-      <c r="U29" s="274"/>
-      <c r="V29" s="274"/>
-      <c r="W29" s="274"/>
-      <c r="X29" s="274"/>
-      <c r="Y29" s="274"/>
-      <c r="Z29" s="274"/>
-      <c r="AA29" s="274"/>
-      <c r="AB29" s="274"/>
-      <c r="AC29" s="274"/>
-      <c r="AD29" s="274"/>
-      <c r="AE29" s="274"/>
-      <c r="AF29" s="275"/>
+      <c r="H29" s="212"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212"/>
+      <c r="L29" s="212"/>
+      <c r="M29" s="212"/>
+      <c r="N29" s="212"/>
+      <c r="O29" s="212"/>
+      <c r="P29" s="212"/>
+      <c r="Q29" s="212"/>
+      <c r="R29" s="212"/>
+      <c r="S29" s="212"/>
+      <c r="T29" s="212"/>
+      <c r="U29" s="212"/>
+      <c r="V29" s="212"/>
+      <c r="W29" s="212"/>
+      <c r="X29" s="212"/>
+      <c r="Y29" s="212"/>
+      <c r="Z29" s="212"/>
+      <c r="AA29" s="212"/>
+      <c r="AB29" s="212"/>
+      <c r="AC29" s="212"/>
+      <c r="AD29" s="212"/>
+      <c r="AE29" s="212"/>
+      <c r="AF29" s="213"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -4901,16 +4901,16 @@
       <c r="AK30" s="10"/>
     </row>
     <row r="31" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="216" t="s">
+      <c r="A31" s="269" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="286" t="s">
+      <c r="B31" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="287"/>
-      <c r="D31" s="287"/>
-      <c r="E31" s="287"/>
-      <c r="F31" s="288"/>
+      <c r="C31" s="129"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="129"/>
+      <c r="F31" s="130"/>
       <c r="G31" s="28" t="s">
         <v>34</v>
       </c>
@@ -4921,21 +4921,21 @@
       <c r="L31" s="22"/>
       <c r="M31" s="10"/>
       <c r="N31" s="42"/>
-      <c r="O31" s="281" t="s">
+      <c r="O31" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="P31" s="130"/>
-      <c r="Q31" s="282" t="s">
+      <c r="P31" s="125"/>
+      <c r="Q31" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="R31" s="282"/>
-      <c r="S31" s="130"/>
-      <c r="T31" s="130"/>
-      <c r="U31" s="130"/>
-      <c r="V31" s="130"/>
-      <c r="W31" s="130"/>
-      <c r="X31" s="130"/>
-      <c r="Y31" s="130"/>
+      <c r="R31" s="126"/>
+      <c r="S31" s="125"/>
+      <c r="T31" s="125"/>
+      <c r="U31" s="125"/>
+      <c r="V31" s="125"/>
+      <c r="W31" s="125"/>
+      <c r="X31" s="125"/>
+      <c r="Y31" s="125"/>
       <c r="Z31" s="83" t="s">
         <v>68</v>
       </c>
@@ -4949,100 +4949,100 @@
       <c r="AK31" s="10"/>
     </row>
     <row r="32" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="217"/>
-      <c r="B32" s="289" t="s">
+      <c r="A32" s="270"/>
+      <c r="B32" s="131" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="290"/>
-      <c r="D32" s="290"/>
-      <c r="E32" s="290"/>
-      <c r="F32" s="291"/>
-      <c r="G32" s="326"/>
-      <c r="H32" s="327"/>
-      <c r="I32" s="327"/>
-      <c r="J32" s="327"/>
-      <c r="K32" s="327"/>
-      <c r="L32" s="327"/>
-      <c r="M32" s="327"/>
-      <c r="N32" s="328"/>
-      <c r="O32" s="326"/>
-      <c r="P32" s="327"/>
-      <c r="Q32" s="327"/>
-      <c r="R32" s="327"/>
-      <c r="S32" s="327"/>
-      <c r="T32" s="327"/>
-      <c r="U32" s="327"/>
-      <c r="V32" s="327"/>
-      <c r="W32" s="327"/>
-      <c r="X32" s="327"/>
-      <c r="Y32" s="327"/>
-      <c r="Z32" s="327"/>
-      <c r="AA32" s="327"/>
-      <c r="AB32" s="327"/>
-      <c r="AC32" s="327"/>
-      <c r="AD32" s="327"/>
-      <c r="AE32" s="327"/>
-      <c r="AF32" s="336"/>
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="99"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="120"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="99"/>
+      <c r="S32" s="99"/>
+      <c r="T32" s="99"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="99"/>
+      <c r="W32" s="99"/>
+      <c r="X32" s="99"/>
+      <c r="Y32" s="99"/>
+      <c r="Z32" s="99"/>
+      <c r="AA32" s="99"/>
+      <c r="AB32" s="99"/>
+      <c r="AC32" s="99"/>
+      <c r="AD32" s="99"/>
+      <c r="AE32" s="99"/>
+      <c r="AF32" s="100"/>
       <c r="AJ32" s="22"/>
       <c r="AK32" s="10"/>
     </row>
     <row r="33" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="217"/>
-      <c r="B33" s="292"/>
-      <c r="C33" s="293"/>
-      <c r="D33" s="293"/>
-      <c r="E33" s="293"/>
-      <c r="F33" s="294"/>
-      <c r="G33" s="329"/>
-      <c r="H33" s="330"/>
-      <c r="I33" s="330"/>
-      <c r="J33" s="330"/>
-      <c r="K33" s="330"/>
-      <c r="L33" s="330"/>
-      <c r="M33" s="330"/>
-      <c r="N33" s="331"/>
+      <c r="A33" s="270"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="122"/>
+      <c r="I33" s="122"/>
+      <c r="J33" s="122"/>
+      <c r="K33" s="122"/>
+      <c r="L33" s="122"/>
+      <c r="M33" s="122"/>
+      <c r="N33" s="123"/>
       <c r="O33" s="37"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="15"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
-      <c r="T33" s="285" t="s">
+      <c r="T33" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U33" s="285"/>
-      <c r="V33" s="285"/>
-      <c r="W33" s="283"/>
-      <c r="X33" s="283"/>
-      <c r="Y33" s="283"/>
-      <c r="Z33" s="283"/>
-      <c r="AA33" s="283"/>
-      <c r="AB33" s="283"/>
-      <c r="AC33" s="283"/>
-      <c r="AD33" s="283"/>
-      <c r="AE33" s="283"/>
-      <c r="AF33" s="284"/>
+      <c r="U33" s="127"/>
+      <c r="V33" s="127"/>
+      <c r="W33" s="101"/>
+      <c r="X33" s="101"/>
+      <c r="Y33" s="101"/>
+      <c r="Z33" s="101"/>
+      <c r="AA33" s="101"/>
+      <c r="AB33" s="101"/>
+      <c r="AC33" s="101"/>
+      <c r="AD33" s="101"/>
+      <c r="AE33" s="101"/>
+      <c r="AF33" s="102"/>
       <c r="AJ33" s="22"/>
       <c r="AK33" s="10"/>
     </row>
     <row r="34" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="217"/>
-      <c r="B34" s="219" t="s">
+      <c r="A34" s="270"/>
+      <c r="B34" s="272" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="219"/>
-      <c r="D34" s="219"/>
-      <c r="E34" s="219"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="332" t="s">
+      <c r="C34" s="272"/>
+      <c r="D34" s="272"/>
+      <c r="E34" s="272"/>
+      <c r="F34" s="273"/>
+      <c r="G34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="333"/>
-      <c r="I34" s="318"/>
-      <c r="J34" s="318"/>
-      <c r="K34" s="318"/>
-      <c r="L34" s="318"/>
-      <c r="M34" s="318"/>
-      <c r="N34" s="319"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="106"/>
       <c r="O34" s="36" t="s">
         <v>9</v>
       </c>
@@ -5064,82 +5064,82 @@
       <c r="AK34" s="10"/>
     </row>
     <row r="35" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="217"/>
-      <c r="B35" s="243" t="s">
+      <c r="A35" s="270"/>
+      <c r="B35" s="173" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="243"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="243"/>
-      <c r="F35" s="244"/>
-      <c r="G35" s="334" t="s">
+      <c r="C35" s="173"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="115" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="335"/>
-      <c r="I35" s="316"/>
-      <c r="J35" s="316"/>
-      <c r="K35" s="316"/>
-      <c r="L35" s="316"/>
-      <c r="M35" s="316"/>
-      <c r="N35" s="317"/>
-      <c r="O35" s="168"/>
-      <c r="P35" s="169"/>
-      <c r="Q35" s="169"/>
-      <c r="R35" s="169"/>
-      <c r="S35" s="268"/>
-      <c r="T35" s="320"/>
-      <c r="U35" s="321"/>
-      <c r="V35" s="321"/>
-      <c r="W35" s="321"/>
-      <c r="X35" s="321"/>
-      <c r="Y35" s="321"/>
-      <c r="Z35" s="321"/>
-      <c r="AA35" s="321"/>
-      <c r="AB35" s="321"/>
-      <c r="AC35" s="321"/>
-      <c r="AD35" s="321"/>
-      <c r="AE35" s="321"/>
-      <c r="AF35" s="322"/>
+      <c r="H35" s="116"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="104"/>
+      <c r="O35" s="107"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="108"/>
+      <c r="S35" s="109"/>
+      <c r="T35" s="110"/>
+      <c r="U35" s="111"/>
+      <c r="V35" s="111"/>
+      <c r="W35" s="111"/>
+      <c r="X35" s="111"/>
+      <c r="Y35" s="111"/>
+      <c r="Z35" s="111"/>
+      <c r="AA35" s="111"/>
+      <c r="AB35" s="111"/>
+      <c r="AC35" s="111"/>
+      <c r="AD35" s="111"/>
+      <c r="AE35" s="111"/>
+      <c r="AF35" s="112"/>
       <c r="AJ35" s="22"/>
       <c r="AK35" s="10"/>
     </row>
     <row r="36" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="217"/>
-      <c r="B36" s="174" t="s">
+      <c r="A36" s="270"/>
+      <c r="B36" s="175" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="174"/>
-      <c r="D36" s="174"/>
-      <c r="E36" s="174"/>
-      <c r="F36" s="175"/>
-      <c r="G36" s="165" t="s">
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="176"/>
+      <c r="G36" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="H36" s="166"/>
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="166"/>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
-      <c r="O36" s="166"/>
-      <c r="P36" s="166"/>
-      <c r="Q36" s="166"/>
-      <c r="R36" s="166"/>
-      <c r="S36" s="166"/>
-      <c r="T36" s="166"/>
-      <c r="U36" s="166"/>
-      <c r="V36" s="166"/>
-      <c r="W36" s="166"/>
-      <c r="X36" s="166"/>
-      <c r="Y36" s="166"/>
-      <c r="Z36" s="166"/>
-      <c r="AA36" s="166"/>
-      <c r="AB36" s="166"/>
-      <c r="AC36" s="166"/>
-      <c r="AD36" s="166"/>
-      <c r="AE36" s="166"/>
-      <c r="AF36" s="167"/>
+      <c r="H36" s="231"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="231"/>
+      <c r="O36" s="231"/>
+      <c r="P36" s="231"/>
+      <c r="Q36" s="231"/>
+      <c r="R36" s="231"/>
+      <c r="S36" s="231"/>
+      <c r="T36" s="231"/>
+      <c r="U36" s="231"/>
+      <c r="V36" s="231"/>
+      <c r="W36" s="231"/>
+      <c r="X36" s="231"/>
+      <c r="Y36" s="231"/>
+      <c r="Z36" s="231"/>
+      <c r="AA36" s="231"/>
+      <c r="AB36" s="231"/>
+      <c r="AC36" s="231"/>
+      <c r="AD36" s="231"/>
+      <c r="AE36" s="231"/>
+      <c r="AF36" s="232"/>
       <c r="AG36" s="8"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8"/>
@@ -5147,40 +5147,40 @@
       <c r="AK36" s="8"/>
     </row>
     <row r="37" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="217"/>
-      <c r="B37" s="209" t="s">
+      <c r="A37" s="270"/>
+      <c r="B37" s="204" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="210"/>
-      <c r="D37" s="210"/>
-      <c r="E37" s="210"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="270"/>
-      <c r="H37" s="271"/>
-      <c r="I37" s="271"/>
-      <c r="J37" s="271"/>
-      <c r="K37" s="271"/>
-      <c r="L37" s="271"/>
-      <c r="M37" s="271"/>
-      <c r="N37" s="271"/>
-      <c r="O37" s="271"/>
-      <c r="P37" s="271"/>
-      <c r="Q37" s="271"/>
-      <c r="R37" s="271"/>
-      <c r="S37" s="271"/>
-      <c r="T37" s="271"/>
-      <c r="U37" s="271"/>
-      <c r="V37" s="271"/>
-      <c r="W37" s="271"/>
-      <c r="X37" s="271"/>
-      <c r="Y37" s="271"/>
-      <c r="Z37" s="271"/>
-      <c r="AA37" s="271"/>
-      <c r="AB37" s="271"/>
-      <c r="AC37" s="271"/>
-      <c r="AD37" s="271"/>
-      <c r="AE37" s="271"/>
-      <c r="AF37" s="272"/>
+      <c r="C37" s="200"/>
+      <c r="D37" s="200"/>
+      <c r="E37" s="200"/>
+      <c r="F37" s="201"/>
+      <c r="G37" s="208"/>
+      <c r="H37" s="209"/>
+      <c r="I37" s="209"/>
+      <c r="J37" s="209"/>
+      <c r="K37" s="209"/>
+      <c r="L37" s="209"/>
+      <c r="M37" s="209"/>
+      <c r="N37" s="209"/>
+      <c r="O37" s="209"/>
+      <c r="P37" s="209"/>
+      <c r="Q37" s="209"/>
+      <c r="R37" s="209"/>
+      <c r="S37" s="209"/>
+      <c r="T37" s="209"/>
+      <c r="U37" s="209"/>
+      <c r="V37" s="209"/>
+      <c r="W37" s="209"/>
+      <c r="X37" s="209"/>
+      <c r="Y37" s="209"/>
+      <c r="Z37" s="209"/>
+      <c r="AA37" s="209"/>
+      <c r="AB37" s="209"/>
+      <c r="AC37" s="209"/>
+      <c r="AD37" s="209"/>
+      <c r="AE37" s="209"/>
+      <c r="AF37" s="210"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
@@ -5188,40 +5188,40 @@
       <c r="AK37" s="8"/>
     </row>
     <row r="38" spans="1:37" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="218"/>
-      <c r="B38" s="211"/>
-      <c r="C38" s="212"/>
-      <c r="D38" s="212"/>
-      <c r="E38" s="212"/>
-      <c r="F38" s="269"/>
-      <c r="G38" s="245" t="s">
+      <c r="A38" s="271"/>
+      <c r="B38" s="205"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="207"/>
+      <c r="G38" s="177" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="246"/>
-      <c r="I38" s="246"/>
-      <c r="J38" s="246"/>
-      <c r="K38" s="246"/>
-      <c r="L38" s="246"/>
-      <c r="M38" s="246"/>
-      <c r="N38" s="246"/>
-      <c r="O38" s="246"/>
-      <c r="P38" s="246"/>
-      <c r="Q38" s="246"/>
-      <c r="R38" s="246"/>
-      <c r="S38" s="246"/>
-      <c r="T38" s="246"/>
-      <c r="U38" s="246"/>
-      <c r="V38" s="246"/>
-      <c r="W38" s="246"/>
-      <c r="X38" s="246"/>
-      <c r="Y38" s="246"/>
-      <c r="Z38" s="246"/>
-      <c r="AA38" s="246"/>
-      <c r="AB38" s="246"/>
-      <c r="AC38" s="246"/>
-      <c r="AD38" s="246"/>
-      <c r="AE38" s="246"/>
-      <c r="AF38" s="247"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178"/>
+      <c r="N38" s="178"/>
+      <c r="O38" s="178"/>
+      <c r="P38" s="178"/>
+      <c r="Q38" s="178"/>
+      <c r="R38" s="178"/>
+      <c r="S38" s="178"/>
+      <c r="T38" s="178"/>
+      <c r="U38" s="178"/>
+      <c r="V38" s="178"/>
+      <c r="W38" s="178"/>
+      <c r="X38" s="178"/>
+      <c r="Y38" s="178"/>
+      <c r="Z38" s="178"/>
+      <c r="AA38" s="178"/>
+      <c r="AB38" s="178"/>
+      <c r="AC38" s="178"/>
+      <c r="AD38" s="178"/>
+      <c r="AE38" s="178"/>
+      <c r="AF38" s="179"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8"/>
@@ -5263,26 +5263,26 @@
       <c r="AF39" s="11"/>
     </row>
     <row r="40" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="185" t="s">
+      <c r="A40" s="241" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="122" t="s">
+      <c r="B40" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="122"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="122"/>
-      <c r="G40" s="281"/>
-      <c r="H40" s="130"/>
-      <c r="I40" s="130"/>
-      <c r="J40" s="130"/>
-      <c r="K40" s="130"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="130"/>
-      <c r="N40" s="130"/>
-      <c r="O40" s="130"/>
-      <c r="P40" s="131"/>
+      <c r="C40" s="180"/>
+      <c r="D40" s="180"/>
+      <c r="E40" s="180"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="125"/>
+      <c r="J40" s="125"/>
+      <c r="K40" s="125"/>
+      <c r="L40" s="125"/>
+      <c r="M40" s="125"/>
+      <c r="N40" s="125"/>
+      <c r="O40" s="125"/>
+      <c r="P40" s="221"/>
       <c r="Q40" s="51" t="s">
         <v>31</v>
       </c>
@@ -5308,31 +5308,31 @@
       <c r="AK40" s="8"/>
     </row>
     <row r="41" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="186"/>
-      <c r="B41" s="132"/>
-      <c r="C41" s="132"/>
-      <c r="D41" s="132"/>
-      <c r="E41" s="132"/>
-      <c r="F41" s="132"/>
-      <c r="G41" s="136"/>
-      <c r="H41" s="132"/>
-      <c r="I41" s="132"/>
-      <c r="J41" s="132"/>
-      <c r="K41" s="132"/>
-      <c r="L41" s="132"/>
-      <c r="M41" s="132"/>
-      <c r="N41" s="132"/>
-      <c r="O41" s="132"/>
-      <c r="P41" s="133"/>
-      <c r="Q41" s="134" t="s">
+      <c r="A41" s="242"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
+      <c r="N41" s="96"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="97"/>
+      <c r="Q41" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="R41" s="135"/>
-      <c r="S41" s="135"/>
-      <c r="T41" s="135"/>
-      <c r="U41" s="135"/>
-      <c r="V41" s="135"/>
-      <c r="W41" s="135"/>
+      <c r="R41" s="93"/>
+      <c r="S41" s="93"/>
+      <c r="T41" s="93"/>
+      <c r="U41" s="93"/>
+      <c r="V41" s="93"/>
+      <c r="W41" s="93"/>
       <c r="X41" s="59" t="s">
         <v>68</v>
       </c>
@@ -5347,80 +5347,80 @@
       <c r="AK41" s="16"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="187"/>
-      <c r="B42" s="206" t="s">
+      <c r="A42" s="243"/>
+      <c r="B42" s="262" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="95"/>
-      <c r="D42" s="95"/>
-      <c r="E42" s="95"/>
-      <c r="F42" s="207"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="135"/>
-      <c r="I42" s="135"/>
-      <c r="J42" s="135"/>
-      <c r="K42" s="135"/>
-      <c r="L42" s="135"/>
-      <c r="M42" s="135"/>
-      <c r="N42" s="135"/>
-      <c r="O42" s="135"/>
-      <c r="P42" s="315"/>
-      <c r="Q42" s="326"/>
-      <c r="R42" s="327"/>
-      <c r="S42" s="327"/>
-      <c r="T42" s="327"/>
-      <c r="U42" s="327"/>
-      <c r="V42" s="327"/>
-      <c r="W42" s="327"/>
-      <c r="X42" s="327"/>
-      <c r="Y42" s="327"/>
-      <c r="Z42" s="327"/>
-      <c r="AA42" s="327"/>
-      <c r="AB42" s="327"/>
-      <c r="AC42" s="327"/>
-      <c r="AD42" s="327"/>
-      <c r="AE42" s="327"/>
-      <c r="AF42" s="336"/>
+      <c r="C42" s="214"/>
+      <c r="D42" s="214"/>
+      <c r="E42" s="214"/>
+      <c r="F42" s="215"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="93"/>
+      <c r="M42" s="93"/>
+      <c r="N42" s="93"/>
+      <c r="O42" s="93"/>
+      <c r="P42" s="94"/>
+      <c r="Q42" s="98"/>
+      <c r="R42" s="99"/>
+      <c r="S42" s="99"/>
+      <c r="T42" s="99"/>
+      <c r="U42" s="99"/>
+      <c r="V42" s="99"/>
+      <c r="W42" s="99"/>
+      <c r="X42" s="99"/>
+      <c r="Y42" s="99"/>
+      <c r="Z42" s="99"/>
+      <c r="AA42" s="99"/>
+      <c r="AB42" s="99"/>
+      <c r="AC42" s="99"/>
+      <c r="AD42" s="99"/>
+      <c r="AE42" s="99"/>
+      <c r="AF42" s="100"/>
       <c r="AK42" s="16"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="187"/>
-      <c r="B43" s="208"/>
-      <c r="C43" s="128"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="128"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="136"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="132"/>
-      <c r="L43" s="132"/>
-      <c r="M43" s="132"/>
-      <c r="N43" s="132"/>
-      <c r="O43" s="132"/>
-      <c r="P43" s="133"/>
+      <c r="A43" s="243"/>
+      <c r="B43" s="263"/>
+      <c r="C43" s="264"/>
+      <c r="D43" s="264"/>
+      <c r="E43" s="264"/>
+      <c r="F43" s="265"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="96"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="96"/>
+      <c r="K43" s="96"/>
+      <c r="L43" s="96"/>
+      <c r="M43" s="96"/>
+      <c r="N43" s="96"/>
+      <c r="O43" s="96"/>
+      <c r="P43" s="97"/>
       <c r="Q43" s="39" t="s">
         <v>3</v>
       </c>
       <c r="R43" s="29"/>
       <c r="S43" s="29"/>
       <c r="T43" s="29"/>
-      <c r="U43" s="283"/>
-      <c r="V43" s="283"/>
-      <c r="W43" s="283"/>
-      <c r="X43" s="283"/>
-      <c r="Y43" s="283"/>
-      <c r="Z43" s="283"/>
-      <c r="AA43" s="283"/>
-      <c r="AB43" s="283"/>
-      <c r="AC43" s="283"/>
-      <c r="AD43" s="283"/>
-      <c r="AE43" s="283"/>
-      <c r="AF43" s="284"/>
+      <c r="U43" s="101"/>
+      <c r="V43" s="101"/>
+      <c r="W43" s="101"/>
+      <c r="X43" s="101"/>
+      <c r="Y43" s="101"/>
+      <c r="Z43" s="101"/>
+      <c r="AA43" s="101"/>
+      <c r="AB43" s="101"/>
+      <c r="AC43" s="101"/>
+      <c r="AD43" s="101"/>
+      <c r="AE43" s="101"/>
+      <c r="AF43" s="102"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="187"/>
+      <c r="A44" s="243"/>
       <c r="B44" s="59" t="s">
         <v>32</v>
       </c>
@@ -5455,7 +5455,7 @@
       <c r="AJ44" s="57"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="187"/>
+      <c r="A45" s="243"/>
       <c r="B45" s="69" t="s">
         <v>33</v>
       </c>
@@ -5491,76 +5491,76 @@
       <c r="AF45" s="6"/>
     </row>
     <row r="46" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="187"/>
-      <c r="B46" s="209" t="s">
+      <c r="A46" s="243"/>
+      <c r="B46" s="204" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="210"/>
-      <c r="D46" s="210"/>
-      <c r="E46" s="210"/>
-      <c r="F46" s="210"/>
-      <c r="G46" s="312"/>
-      <c r="H46" s="313"/>
-      <c r="I46" s="313"/>
-      <c r="J46" s="313"/>
-      <c r="K46" s="313"/>
-      <c r="L46" s="313"/>
-      <c r="M46" s="313"/>
-      <c r="N46" s="313"/>
-      <c r="O46" s="313"/>
-      <c r="P46" s="313"/>
-      <c r="Q46" s="313"/>
-      <c r="R46" s="313"/>
-      <c r="S46" s="313"/>
-      <c r="T46" s="313"/>
-      <c r="U46" s="313"/>
-      <c r="V46" s="313"/>
-      <c r="W46" s="313"/>
-      <c r="X46" s="313"/>
-      <c r="Y46" s="313"/>
-      <c r="Z46" s="313"/>
-      <c r="AA46" s="313"/>
-      <c r="AB46" s="313"/>
-      <c r="AC46" s="313"/>
-      <c r="AD46" s="313"/>
-      <c r="AE46" s="313"/>
-      <c r="AF46" s="314"/>
+      <c r="C46" s="200"/>
+      <c r="D46" s="200"/>
+      <c r="E46" s="200"/>
+      <c r="F46" s="200"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="219"/>
+      <c r="I46" s="219"/>
+      <c r="J46" s="219"/>
+      <c r="K46" s="219"/>
+      <c r="L46" s="219"/>
+      <c r="M46" s="219"/>
+      <c r="N46" s="219"/>
+      <c r="O46" s="219"/>
+      <c r="P46" s="219"/>
+      <c r="Q46" s="219"/>
+      <c r="R46" s="219"/>
+      <c r="S46" s="219"/>
+      <c r="T46" s="219"/>
+      <c r="U46" s="219"/>
+      <c r="V46" s="219"/>
+      <c r="W46" s="219"/>
+      <c r="X46" s="219"/>
+      <c r="Y46" s="219"/>
+      <c r="Z46" s="219"/>
+      <c r="AA46" s="219"/>
+      <c r="AB46" s="219"/>
+      <c r="AC46" s="219"/>
+      <c r="AD46" s="219"/>
+      <c r="AE46" s="219"/>
+      <c r="AF46" s="220"/>
     </row>
     <row r="47" spans="1:37" s="52" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="188"/>
-      <c r="B47" s="211"/>
-      <c r="C47" s="212"/>
-      <c r="D47" s="212"/>
-      <c r="E47" s="212"/>
-      <c r="F47" s="212"/>
-      <c r="G47" s="213" t="s">
+      <c r="A47" s="244"/>
+      <c r="B47" s="205"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
+      <c r="F47" s="206"/>
+      <c r="G47" s="266" t="s">
         <v>28</v>
       </c>
-      <c r="H47" s="214"/>
-      <c r="I47" s="214"/>
-      <c r="J47" s="214"/>
-      <c r="K47" s="214"/>
-      <c r="L47" s="214"/>
-      <c r="M47" s="214"/>
-      <c r="N47" s="214"/>
-      <c r="O47" s="214"/>
-      <c r="P47" s="214"/>
-      <c r="Q47" s="214"/>
-      <c r="R47" s="214"/>
-      <c r="S47" s="214"/>
-      <c r="T47" s="214"/>
-      <c r="U47" s="214"/>
-      <c r="V47" s="214"/>
-      <c r="W47" s="214"/>
-      <c r="X47" s="214"/>
-      <c r="Y47" s="214"/>
-      <c r="Z47" s="214"/>
-      <c r="AA47" s="214"/>
-      <c r="AB47" s="214"/>
-      <c r="AC47" s="214"/>
-      <c r="AD47" s="214"/>
-      <c r="AE47" s="214"/>
-      <c r="AF47" s="215"/>
+      <c r="H47" s="267"/>
+      <c r="I47" s="267"/>
+      <c r="J47" s="267"/>
+      <c r="K47" s="267"/>
+      <c r="L47" s="267"/>
+      <c r="M47" s="267"/>
+      <c r="N47" s="267"/>
+      <c r="O47" s="267"/>
+      <c r="P47" s="267"/>
+      <c r="Q47" s="267"/>
+      <c r="R47" s="267"/>
+      <c r="S47" s="267"/>
+      <c r="T47" s="267"/>
+      <c r="U47" s="267"/>
+      <c r="V47" s="267"/>
+      <c r="W47" s="267"/>
+      <c r="X47" s="267"/>
+      <c r="Y47" s="267"/>
+      <c r="Z47" s="267"/>
+      <c r="AA47" s="267"/>
+      <c r="AB47" s="267"/>
+      <c r="AC47" s="267"/>
+      <c r="AD47" s="267"/>
+      <c r="AE47" s="267"/>
+      <c r="AF47" s="268"/>
       <c r="AJ47" s="58"/>
     </row>
     <row r="48" spans="1:37" s="21" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5601,301 +5601,301 @@
       <c r="D49" s="74"/>
       <c r="E49" s="74"/>
       <c r="F49" s="75"/>
-      <c r="G49" s="231" t="s">
+      <c r="G49" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="232"/>
-      <c r="I49" s="232"/>
-      <c r="J49" s="232"/>
-      <c r="K49" s="232"/>
-      <c r="L49" s="232"/>
-      <c r="M49" s="232"/>
-      <c r="N49" s="232"/>
-      <c r="O49" s="232"/>
-      <c r="P49" s="232"/>
-      <c r="Q49" s="232"/>
-      <c r="R49" s="232"/>
-      <c r="S49" s="232"/>
-      <c r="T49" s="232"/>
-      <c r="U49" s="232"/>
-      <c r="V49" s="232"/>
-      <c r="W49" s="232"/>
-      <c r="X49" s="232"/>
-      <c r="Y49" s="232"/>
-      <c r="Z49" s="232"/>
-      <c r="AA49" s="232"/>
-      <c r="AB49" s="232"/>
-      <c r="AC49" s="232"/>
-      <c r="AD49" s="232"/>
-      <c r="AE49" s="232"/>
-      <c r="AF49" s="233"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="162"/>
+      <c r="K49" s="162"/>
+      <c r="L49" s="162"/>
+      <c r="M49" s="162"/>
+      <c r="N49" s="162"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="162"/>
+      <c r="Q49" s="162"/>
+      <c r="R49" s="162"/>
+      <c r="S49" s="162"/>
+      <c r="T49" s="162"/>
+      <c r="U49" s="162"/>
+      <c r="V49" s="162"/>
+      <c r="W49" s="162"/>
+      <c r="X49" s="162"/>
+      <c r="Y49" s="162"/>
+      <c r="Z49" s="162"/>
+      <c r="AA49" s="162"/>
+      <c r="AB49" s="162"/>
+      <c r="AC49" s="162"/>
+      <c r="AD49" s="162"/>
+      <c r="AE49" s="162"/>
+      <c r="AF49" s="163"/>
       <c r="AG49" s="30"/>
     </row>
     <row r="50" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="162" t="s">
+      <c r="B50" s="227" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="163"/>
-      <c r="D50" s="163"/>
-      <c r="E50" s="164"/>
+      <c r="C50" s="228"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="229"/>
       <c r="F50" s="75"/>
-      <c r="G50" s="234"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="235"/>
-      <c r="T50" s="235"/>
-      <c r="U50" s="235"/>
-      <c r="V50" s="235"/>
-      <c r="W50" s="235"/>
-      <c r="X50" s="235"/>
-      <c r="Y50" s="235"/>
-      <c r="Z50" s="235"/>
-      <c r="AA50" s="235"/>
-      <c r="AB50" s="235"/>
-      <c r="AC50" s="235"/>
-      <c r="AD50" s="235"/>
-      <c r="AE50" s="235"/>
-      <c r="AF50" s="236"/>
+      <c r="G50" s="164"/>
+      <c r="H50" s="165"/>
+      <c r="I50" s="165"/>
+      <c r="J50" s="165"/>
+      <c r="K50" s="165"/>
+      <c r="L50" s="165"/>
+      <c r="M50" s="165"/>
+      <c r="N50" s="165"/>
+      <c r="O50" s="165"/>
+      <c r="P50" s="165"/>
+      <c r="Q50" s="165"/>
+      <c r="R50" s="165"/>
+      <c r="S50" s="165"/>
+      <c r="T50" s="165"/>
+      <c r="U50" s="165"/>
+      <c r="V50" s="165"/>
+      <c r="W50" s="165"/>
+      <c r="X50" s="165"/>
+      <c r="Y50" s="165"/>
+      <c r="Z50" s="165"/>
+      <c r="AA50" s="165"/>
+      <c r="AB50" s="165"/>
+      <c r="AC50" s="165"/>
+      <c r="AD50" s="165"/>
+      <c r="AE50" s="165"/>
+      <c r="AF50" s="166"/>
       <c r="AG50" s="30"/>
     </row>
     <row r="51" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="189" t="s">
+      <c r="A51" s="245" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="192" t="s">
+      <c r="B51" s="248" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="194" t="s">
+      <c r="C51" s="250" t="s">
         <v>44</v>
       </c>
-      <c r="D51" s="195"/>
-      <c r="E51" s="196"/>
+      <c r="D51" s="251"/>
+      <c r="E51" s="252"/>
       <c r="F51" s="75"/>
-      <c r="G51" s="234"/>
-      <c r="H51" s="235"/>
-      <c r="I51" s="235"/>
-      <c r="J51" s="235"/>
-      <c r="K51" s="235"/>
-      <c r="L51" s="235"/>
-      <c r="M51" s="235"/>
-      <c r="N51" s="235"/>
-      <c r="O51" s="235"/>
-      <c r="P51" s="235"/>
-      <c r="Q51" s="235"/>
-      <c r="R51" s="235"/>
-      <c r="S51" s="235"/>
-      <c r="T51" s="235"/>
-      <c r="U51" s="235"/>
-      <c r="V51" s="235"/>
-      <c r="W51" s="235"/>
-      <c r="X51" s="235"/>
-      <c r="Y51" s="235"/>
-      <c r="Z51" s="235"/>
-      <c r="AA51" s="235"/>
-      <c r="AB51" s="235"/>
-      <c r="AC51" s="235"/>
-      <c r="AD51" s="235"/>
-      <c r="AE51" s="235"/>
-      <c r="AF51" s="236"/>
+      <c r="G51" s="164"/>
+      <c r="H51" s="165"/>
+      <c r="I51" s="165"/>
+      <c r="J51" s="165"/>
+      <c r="K51" s="165"/>
+      <c r="L51" s="165"/>
+      <c r="M51" s="165"/>
+      <c r="N51" s="165"/>
+      <c r="O51" s="165"/>
+      <c r="P51" s="165"/>
+      <c r="Q51" s="165"/>
+      <c r="R51" s="165"/>
+      <c r="S51" s="165"/>
+      <c r="T51" s="165"/>
+      <c r="U51" s="165"/>
+      <c r="V51" s="165"/>
+      <c r="W51" s="165"/>
+      <c r="X51" s="165"/>
+      <c r="Y51" s="165"/>
+      <c r="Z51" s="165"/>
+      <c r="AA51" s="165"/>
+      <c r="AB51" s="165"/>
+      <c r="AC51" s="165"/>
+      <c r="AD51" s="165"/>
+      <c r="AE51" s="165"/>
+      <c r="AF51" s="166"/>
       <c r="AG51" s="30"/>
     </row>
     <row r="52" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="190"/>
-      <c r="B52" s="193"/>
-      <c r="C52" s="197"/>
-      <c r="D52" s="198"/>
-      <c r="E52" s="199"/>
+      <c r="A52" s="246"/>
+      <c r="B52" s="249"/>
+      <c r="C52" s="253"/>
+      <c r="D52" s="254"/>
+      <c r="E52" s="255"/>
       <c r="F52" s="75"/>
-      <c r="G52" s="234"/>
-      <c r="H52" s="235"/>
-      <c r="I52" s="235"/>
-      <c r="J52" s="235"/>
-      <c r="K52" s="235"/>
-      <c r="L52" s="235"/>
-      <c r="M52" s="235"/>
-      <c r="N52" s="235"/>
-      <c r="O52" s="235"/>
-      <c r="P52" s="235"/>
-      <c r="Q52" s="235"/>
-      <c r="R52" s="235"/>
-      <c r="S52" s="235"/>
-      <c r="T52" s="235"/>
-      <c r="U52" s="235"/>
-      <c r="V52" s="235"/>
-      <c r="W52" s="235"/>
-      <c r="X52" s="235"/>
-      <c r="Y52" s="235"/>
-      <c r="Z52" s="235"/>
-      <c r="AA52" s="235"/>
-      <c r="AB52" s="235"/>
-      <c r="AC52" s="235"/>
-      <c r="AD52" s="235"/>
-      <c r="AE52" s="235"/>
-      <c r="AF52" s="236"/>
+      <c r="G52" s="164"/>
+      <c r="H52" s="165"/>
+      <c r="I52" s="165"/>
+      <c r="J52" s="165"/>
+      <c r="K52" s="165"/>
+      <c r="L52" s="165"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="165"/>
+      <c r="O52" s="165"/>
+      <c r="P52" s="165"/>
+      <c r="Q52" s="165"/>
+      <c r="R52" s="165"/>
+      <c r="S52" s="165"/>
+      <c r="T52" s="165"/>
+      <c r="U52" s="165"/>
+      <c r="V52" s="165"/>
+      <c r="W52" s="165"/>
+      <c r="X52" s="165"/>
+      <c r="Y52" s="165"/>
+      <c r="Z52" s="165"/>
+      <c r="AA52" s="165"/>
+      <c r="AB52" s="165"/>
+      <c r="AC52" s="165"/>
+      <c r="AD52" s="165"/>
+      <c r="AE52" s="165"/>
+      <c r="AF52" s="166"/>
       <c r="AG52" s="30"/>
     </row>
     <row r="53" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="190"/>
-      <c r="B53" s="192" t="s">
+      <c r="A53" s="246"/>
+      <c r="B53" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="194" t="s">
+      <c r="C53" s="250" t="s">
         <v>41</v>
       </c>
-      <c r="D53" s="195"/>
-      <c r="E53" s="196"/>
+      <c r="D53" s="251"/>
+      <c r="E53" s="252"/>
       <c r="F53" s="75"/>
-      <c r="G53" s="234"/>
-      <c r="H53" s="235"/>
-      <c r="I53" s="235"/>
-      <c r="J53" s="235"/>
-      <c r="K53" s="235"/>
-      <c r="L53" s="235"/>
-      <c r="M53" s="235"/>
-      <c r="N53" s="235"/>
-      <c r="O53" s="235"/>
-      <c r="P53" s="235"/>
-      <c r="Q53" s="235"/>
-      <c r="R53" s="235"/>
-      <c r="S53" s="235"/>
-      <c r="T53" s="235"/>
-      <c r="U53" s="235"/>
-      <c r="V53" s="235"/>
-      <c r="W53" s="235"/>
-      <c r="X53" s="235"/>
-      <c r="Y53" s="235"/>
-      <c r="Z53" s="235"/>
-      <c r="AA53" s="235"/>
-      <c r="AB53" s="235"/>
-      <c r="AC53" s="235"/>
-      <c r="AD53" s="235"/>
-      <c r="AE53" s="235"/>
-      <c r="AF53" s="236"/>
+      <c r="G53" s="164"/>
+      <c r="H53" s="165"/>
+      <c r="I53" s="165"/>
+      <c r="J53" s="165"/>
+      <c r="K53" s="165"/>
+      <c r="L53" s="165"/>
+      <c r="M53" s="165"/>
+      <c r="N53" s="165"/>
+      <c r="O53" s="165"/>
+      <c r="P53" s="165"/>
+      <c r="Q53" s="165"/>
+      <c r="R53" s="165"/>
+      <c r="S53" s="165"/>
+      <c r="T53" s="165"/>
+      <c r="U53" s="165"/>
+      <c r="V53" s="165"/>
+      <c r="W53" s="165"/>
+      <c r="X53" s="165"/>
+      <c r="Y53" s="165"/>
+      <c r="Z53" s="165"/>
+      <c r="AA53" s="165"/>
+      <c r="AB53" s="165"/>
+      <c r="AC53" s="165"/>
+      <c r="AD53" s="165"/>
+      <c r="AE53" s="165"/>
+      <c r="AF53" s="166"/>
       <c r="AG53" s="30"/>
     </row>
     <row r="54" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="190"/>
-      <c r="B54" s="200"/>
-      <c r="C54" s="197"/>
-      <c r="D54" s="198"/>
-      <c r="E54" s="199"/>
+      <c r="A54" s="246"/>
+      <c r="B54" s="256"/>
+      <c r="C54" s="253"/>
+      <c r="D54" s="254"/>
+      <c r="E54" s="255"/>
       <c r="F54" s="75"/>
-      <c r="G54" s="237" t="s">
+      <c r="G54" s="167" t="s">
         <v>47</v>
       </c>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="238"/>
-      <c r="T54" s="238"/>
-      <c r="U54" s="238"/>
-      <c r="V54" s="238"/>
-      <c r="W54" s="238"/>
-      <c r="X54" s="238"/>
-      <c r="Y54" s="238"/>
-      <c r="Z54" s="238"/>
-      <c r="AA54" s="238"/>
-      <c r="AB54" s="238"/>
-      <c r="AC54" s="238"/>
-      <c r="AD54" s="238"/>
-      <c r="AE54" s="238"/>
-      <c r="AF54" s="239"/>
+      <c r="H54" s="168"/>
+      <c r="I54" s="168"/>
+      <c r="J54" s="168"/>
+      <c r="K54" s="168"/>
+      <c r="L54" s="168"/>
+      <c r="M54" s="168"/>
+      <c r="N54" s="168"/>
+      <c r="O54" s="168"/>
+      <c r="P54" s="168"/>
+      <c r="Q54" s="168"/>
+      <c r="R54" s="168"/>
+      <c r="S54" s="168"/>
+      <c r="T54" s="168"/>
+      <c r="U54" s="168"/>
+      <c r="V54" s="168"/>
+      <c r="W54" s="168"/>
+      <c r="X54" s="168"/>
+      <c r="Y54" s="168"/>
+      <c r="Z54" s="168"/>
+      <c r="AA54" s="168"/>
+      <c r="AB54" s="168"/>
+      <c r="AC54" s="168"/>
+      <c r="AD54" s="168"/>
+      <c r="AE54" s="168"/>
+      <c r="AF54" s="169"/>
       <c r="AG54" s="30"/>
     </row>
     <row r="55" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="190"/>
-      <c r="B55" s="201" t="s">
+      <c r="A55" s="246"/>
+      <c r="B55" s="257" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="203" t="s">
+      <c r="C55" s="259" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="204"/>
-      <c r="E55" s="205"/>
+      <c r="D55" s="260"/>
+      <c r="E55" s="261"/>
       <c r="F55" s="75"/>
-      <c r="G55" s="240"/>
-      <c r="H55" s="241"/>
-      <c r="I55" s="241"/>
-      <c r="J55" s="241"/>
-      <c r="K55" s="241"/>
-      <c r="L55" s="241"/>
-      <c r="M55" s="241"/>
-      <c r="N55" s="241"/>
-      <c r="O55" s="241"/>
-      <c r="P55" s="241"/>
-      <c r="Q55" s="241"/>
-      <c r="R55" s="241"/>
-      <c r="S55" s="241"/>
-      <c r="T55" s="241"/>
-      <c r="U55" s="241"/>
-      <c r="V55" s="241"/>
-      <c r="W55" s="241"/>
-      <c r="X55" s="241"/>
-      <c r="Y55" s="241"/>
-      <c r="Z55" s="241"/>
-      <c r="AA55" s="241"/>
-      <c r="AB55" s="241"/>
-      <c r="AC55" s="241"/>
-      <c r="AD55" s="241"/>
-      <c r="AE55" s="241"/>
-      <c r="AF55" s="242"/>
+      <c r="G55" s="170"/>
+      <c r="H55" s="171"/>
+      <c r="I55" s="171"/>
+      <c r="J55" s="171"/>
+      <c r="K55" s="171"/>
+      <c r="L55" s="171"/>
+      <c r="M55" s="171"/>
+      <c r="N55" s="171"/>
+      <c r="O55" s="171"/>
+      <c r="P55" s="171"/>
+      <c r="Q55" s="171"/>
+      <c r="R55" s="171"/>
+      <c r="S55" s="171"/>
+      <c r="T55" s="171"/>
+      <c r="U55" s="171"/>
+      <c r="V55" s="171"/>
+      <c r="W55" s="171"/>
+      <c r="X55" s="171"/>
+      <c r="Y55" s="171"/>
+      <c r="Z55" s="171"/>
+      <c r="AA55" s="171"/>
+      <c r="AB55" s="171"/>
+      <c r="AC55" s="171"/>
+      <c r="AD55" s="171"/>
+      <c r="AE55" s="171"/>
+      <c r="AF55" s="172"/>
       <c r="AG55" s="30"/>
     </row>
     <row r="56" spans="1:33" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="191"/>
-      <c r="B56" s="202"/>
-      <c r="C56" s="197"/>
-      <c r="D56" s="198"/>
-      <c r="E56" s="199"/>
+      <c r="A56" s="247"/>
+      <c r="B56" s="258"/>
+      <c r="C56" s="253"/>
+      <c r="D56" s="254"/>
+      <c r="E56" s="255"/>
       <c r="F56" s="76"/>
-      <c r="G56" s="157" t="s">
+      <c r="G56" s="222" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="158"/>
-      <c r="I56" s="158"/>
-      <c r="J56" s="158"/>
-      <c r="K56" s="158"/>
-      <c r="L56" s="158"/>
-      <c r="M56" s="158"/>
-      <c r="N56" s="158"/>
-      <c r="O56" s="158"/>
-      <c r="P56" s="158"/>
-      <c r="Q56" s="158"/>
-      <c r="R56" s="158"/>
-      <c r="S56" s="158"/>
-      <c r="T56" s="158"/>
-      <c r="U56" s="158"/>
-      <c r="V56" s="158"/>
-      <c r="W56" s="158"/>
-      <c r="X56" s="158"/>
-      <c r="Y56" s="158"/>
-      <c r="Z56" s="158"/>
-      <c r="AA56" s="158"/>
-      <c r="AB56" s="158"/>
-      <c r="AC56" s="158"/>
-      <c r="AD56" s="158"/>
-      <c r="AE56" s="158"/>
-      <c r="AF56" s="159"/>
+      <c r="H56" s="223"/>
+      <c r="I56" s="223"/>
+      <c r="J56" s="223"/>
+      <c r="K56" s="223"/>
+      <c r="L56" s="223"/>
+      <c r="M56" s="223"/>
+      <c r="N56" s="223"/>
+      <c r="O56" s="223"/>
+      <c r="P56" s="223"/>
+      <c r="Q56" s="223"/>
+      <c r="R56" s="223"/>
+      <c r="S56" s="223"/>
+      <c r="T56" s="223"/>
+      <c r="U56" s="223"/>
+      <c r="V56" s="223"/>
+      <c r="W56" s="223"/>
+      <c r="X56" s="223"/>
+      <c r="Y56" s="223"/>
+      <c r="Z56" s="223"/>
+      <c r="AA56" s="223"/>
+      <c r="AB56" s="223"/>
+      <c r="AC56" s="223"/>
+      <c r="AD56" s="223"/>
+      <c r="AE56" s="223"/>
+      <c r="AF56" s="224"/>
     </row>
     <row r="57" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="60" t="s">
@@ -5923,39 +5923,60 @@
       <c r="AF57" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="G42:P43"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:W41"/>
-    <mergeCell ref="Q42:AF42"/>
-    <mergeCell ref="U43:AF43"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="O35:S35"/>
-    <mergeCell ref="T35:AF35"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="A16:A29"/>
-    <mergeCell ref="G32:N33"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:Y31"/>
-    <mergeCell ref="O32:AF32"/>
-    <mergeCell ref="W33:AF33"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F33"/>
-    <mergeCell ref="G22:J23"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="N22:AF22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="G24:J25"/>
-    <mergeCell ref="N23:U23"/>
-    <mergeCell ref="W23:AF23"/>
-    <mergeCell ref="K24:R24"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="K25:V25"/>
-    <mergeCell ref="U21:X21"/>
+  <mergeCells count="112">
+    <mergeCell ref="G28:AF28"/>
+    <mergeCell ref="B26:F27"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="V26:Z26"/>
+    <mergeCell ref="V27:X27"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="AA26:AF26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="A8:C12"/>
+    <mergeCell ref="T7:W8"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="G12:R12"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="G14:P14"/>
+    <mergeCell ref="W14:AF14"/>
+    <mergeCell ref="X12:AF12"/>
+    <mergeCell ref="G9:S10"/>
+    <mergeCell ref="T9:W10"/>
+    <mergeCell ref="X9:AF10"/>
+    <mergeCell ref="X7:AF8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G56:AF56"/>
+    <mergeCell ref="AD1:AF2"/>
+    <mergeCell ref="B3:X5"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="G36:AF36"/>
+    <mergeCell ref="U17:AF17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:E56"/>
+    <mergeCell ref="B42:F43"/>
+    <mergeCell ref="B46:F47"/>
+    <mergeCell ref="G47:AF47"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="G49:AF53"/>
     <mergeCell ref="G54:AF55"/>
     <mergeCell ref="B35:F35"/>
@@ -5978,65 +5999,43 @@
     <mergeCell ref="B28:F29"/>
     <mergeCell ref="G46:AF46"/>
     <mergeCell ref="G40:P41"/>
-    <mergeCell ref="G56:AF56"/>
-    <mergeCell ref="AD1:AF2"/>
-    <mergeCell ref="B3:X5"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="G36:AF36"/>
-    <mergeCell ref="U17:AF17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:AF13"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:E56"/>
-    <mergeCell ref="B42:F43"/>
-    <mergeCell ref="B46:F47"/>
-    <mergeCell ref="G47:AF47"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="B34:F34"/>
     <mergeCell ref="W25:AF25"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="A8:C12"/>
-    <mergeCell ref="T7:W8"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="G12:R12"/>
-    <mergeCell ref="G8:S8"/>
-    <mergeCell ref="G14:P14"/>
-    <mergeCell ref="W14:AF14"/>
-    <mergeCell ref="X12:AF12"/>
-    <mergeCell ref="G9:S10"/>
-    <mergeCell ref="T9:W10"/>
-    <mergeCell ref="X9:AF10"/>
-    <mergeCell ref="X7:AF8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
     <mergeCell ref="U18:AF18"/>
+    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="G32:N33"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S31:Y31"/>
+    <mergeCell ref="O32:AF32"/>
+    <mergeCell ref="W33:AF33"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F33"/>
+    <mergeCell ref="G22:J23"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="N22:AF22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="G24:J25"/>
+    <mergeCell ref="N23:U23"/>
+    <mergeCell ref="W23:AF23"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="S24:AF24"/>
+    <mergeCell ref="K25:V25"/>
+    <mergeCell ref="U21:X21"/>
     <mergeCell ref="H19:L19"/>
     <mergeCell ref="G20:T21"/>
     <mergeCell ref="Y21:AF21"/>
-    <mergeCell ref="G28:AF28"/>
-    <mergeCell ref="B26:F27"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="V26:Z26"/>
-    <mergeCell ref="V27:X27"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="AA26:AF26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="G42:P43"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:W41"/>
+    <mergeCell ref="Q42:AF42"/>
+    <mergeCell ref="U43:AF43"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="O35:S35"/>
+    <mergeCell ref="T35:AF35"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
